--- a/intern_schedule_2026-2027/schedules/TYP_May_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_May_2027.xlsx
@@ -517,13 +517,13 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH  (24H)</t>
+          <t>GABALLAH B  (24H)</t>
         </is>
       </c>
     </row>
@@ -538,13 +538,13 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -559,17 +559,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>GABALLAH, AHLUWALIA</t>
+          <t>GABALLAH B, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -584,17 +584,17 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>BRONSON, AHLUWALIA</t>
+          <t>BRONSON I, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -609,17 +609,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>BRONSON, GABALLAH</t>
+          <t>BRONSON I, GABALLAH B</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -634,17 +634,17 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -659,17 +659,17 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>GABALLAH, AHLUWALIA</t>
+          <t>GABALLAH B, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
     </row>
@@ -684,13 +684,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D10" s="3" t="n"/>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA  (24H)</t>
+          <t>AHLUWALIA Sa  (24H)</t>
         </is>
       </c>
     </row>
@@ -705,13 +705,13 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>GABALLAH</t>
+          <t>GABALLAH B</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -726,17 +726,17 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>METRI, AHLUWALIA</t>
+          <t>METRI N, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -751,17 +751,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>LI, AHLUWALIA</t>
+          <t>LI A, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -776,17 +776,17 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>LI, METRI</t>
+          <t>LI A, METRI N</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -801,17 +801,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -826,17 +826,17 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>METRI, AHLUWALIA</t>
+          <t>METRI N, AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
     </row>
@@ -851,13 +851,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA  (24H)</t>
+          <t>AHLUWALIA Sa  (24H)</t>
         </is>
       </c>
     </row>
@@ -872,13 +872,13 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -893,17 +893,17 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>BRONSON, SANCHEZ-ALMANZAR</t>
+          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -918,17 +918,17 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>LI, BRONSON</t>
+          <t>LI A, BRONSON I</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -943,17 +943,17 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>LI, SANCHEZ-ALMANZAR</t>
+          <t>LI A, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -968,17 +968,17 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>LI, SANCHEZ-ALMANZAR</t>
+          <t>LI A, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
     </row>
@@ -1018,13 +1018,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>LI  (24H)</t>
+          <t>LI A  (24H)</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1039,13 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>METRI</t>
+          <t>METRI N</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>LI, SAEED</t>
+          <t>LI A, SAEED S</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1085,17 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>LI, BRONSON</t>
+          <t>LI A, BRONSON I</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -1110,17 +1110,17 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>BRONSON, SAEED</t>
+          <t>BRONSON I, SAEED S</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -1135,17 +1135,17 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -1160,17 +1160,17 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>LI, BRONSON</t>
+          <t>LI A, BRONSON I</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1185,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>BRONSON</t>
+          <t>BRONSON I</t>
         </is>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>BRONSON  (24H)</t>
+          <t>BRONSON I  (24H)</t>
         </is>
       </c>
     </row>
@@ -1206,13 +1206,13 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR</t>
+          <t>SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>
@@ -1227,17 +1227,17 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>LI</t>
+          <t>LI A</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>BRONSON, SANCHEZ-ALMANZAR</t>
+          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>SAEED</t>
+          <t>SAEED S</t>
         </is>
       </c>
     </row>

--- a/intern_schedule_2026-2027/schedules/TYP_May_2027.xlsx
+++ b/intern_schedule_2026-2027/schedules/TYP_May_2027.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <b val="1"/>
       <i val="1"/>
@@ -78,23 +79,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,13 +521,13 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH B</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D3" s="3" t="n"/>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>GABALLAH B  (24H)</t>
+          <t>LI  (24H)</t>
         </is>
       </c>
     </row>
@@ -544,7 +548,7 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>LI A</t>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -557,19 +561,19 @@
       <c r="B5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>GABALLAH B, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>LI, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -582,19 +586,19 @@
       <c r="B6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -607,19 +611,19 @@
       <c r="B7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I, GABALLAH B</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON, LI</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -632,19 +636,19 @@
       <c r="B8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>GABALLAH B</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -657,19 +661,19 @@
       <c r="B9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>GABALLAH B, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>GABALLAH</t>
         </is>
       </c>
     </row>
@@ -705,13 +709,13 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>GABALLAH B</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>BRONSON I</t>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -724,19 +728,19 @@
       <c r="B12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>METRI N, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa, BRONSON</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -749,19 +753,19 @@
       <c r="B13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>LI A, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>METRI, BRONSON</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -774,19 +778,19 @@
       <c r="B14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>LI A, METRI N</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>METRI, AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -799,19 +803,19 @@
       <c r="B15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
         <is>
           <t>AHLUWALIA Sa</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -824,19 +828,19 @@
       <c r="B16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>METRI N, AHLUWALIA Sa</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>AHLUWALIA Sa</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>METRI, BRONSON</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
         </is>
       </c>
     </row>
@@ -851,13 +855,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sa</t>
+          <t>BRONSON</t>
         </is>
       </c>
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>AHLUWALIA Sa  (24H)</t>
+          <t>BRONSON  (24H)</t>
         </is>
       </c>
     </row>
@@ -872,13 +876,13 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>BRONSON I</t>
+          <t>METRI</t>
         </is>
       </c>
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>METRI N</t>
+          <t>AHLUWALIA Sa</t>
         </is>
       </c>
     </row>
@@ -891,19 +895,19 @@
       <c r="B19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON, METRI</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -916,19 +920,19 @@
       <c r="B20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>LI A, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>LI, METRI</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -941,19 +945,19 @@
       <c r="B21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>LI A, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>METRI</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>LI, BRONSON</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -966,19 +970,19 @@
       <c r="B22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -991,19 +995,19 @@
       <c r="B23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>LI A, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>METRI N</t>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>LI, METRI</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
     </row>
@@ -1018,13 +1022,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>LI A</t>
+          <t>METRI</t>
         </is>
       </c>
       <c r="D24" s="3" t="n"/>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>LI A  (24H)</t>
+          <t>METRI  (24H)</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1043,13 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>METRI N</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1058,19 +1062,19 @@
       <c r="B26" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>LI A, SAEED S</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>SAEED Sh, LI</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1083,19 +1087,19 @@
       <c r="B27" s="5" t="n">
         <v>25</v>
       </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>LI A, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR, LI</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1108,19 +1112,19 @@
       <c r="B28" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I, SAEED S</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>LI</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR, SAEED Sh</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1133,19 +1137,19 @@
       <c r="B29" s="5" t="n">
         <v>27</v>
       </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1158,19 +1162,19 @@
       <c r="B30" s="5" t="n">
         <v>28</v>
       </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>LI A, BRONSON I</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>SANCHEZ-ALMANZAR, LI</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
         </is>
       </c>
     </row>
@@ -1185,13 +1189,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>BRONSON I</t>
+          <t>LI</t>
         </is>
       </c>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>BRONSON I  (24H)</t>
+          <t>LI  (24H)</t>
         </is>
       </c>
     </row>
@@ -1206,13 +1210,13 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>SANCHEZ-ALMANZAR D</t>
+          <t>SANCHEZ-ALMANZAR</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>SAEED S</t>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
@@ -1225,36 +1229,36 @@
       <c r="B33" s="5" t="n">
         <v>31</v>
       </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>LI A</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>BRONSON I, SANCHEZ-ALMANZAR D</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>SAEED S</t>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>BRONSON</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>LI, SANCHEZ-ALMANZAR</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>SAEED Sh</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>INTERNS</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>DATES</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>LSH</t>
         </is>
@@ -1285,7 +1289,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>BMC-S / BRIGHTON</t>
         </is>
@@ -1328,7 +1332,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>LAHEY</t>
         </is>
@@ -1359,7 +1363,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>SENIOR RESIDENT</t>
         </is>
@@ -1402,7 +1406,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>SHORT CALL DOESN'T LEAVE BEFORE 4 PM, UNLESS APPROVED BY PD/APDS</t>
         </is>
